--- a/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
+++ b/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Knowledge_Hub/02.FOMD/02.metadata_structure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A91F50A-CEB9-4E78-8A4B-44E4412D191A}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3D703AA-CD71-4C29-8D6D-BF3C621E57D2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
+    <workbookView minimized="1" xWindow="30060" yWindow="1815" windowWidth="21600" windowHeight="11175" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
   </bookViews>
   <sheets>
     <sheet name="00_FOMD_Roses" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>MD_Rosen_24_Effec_Sc</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>MD_Jones_21_A glo_Sc</t>
+  </si>
+  <si>
+    <t>MD_Paut,_24_A glo_Sc</t>
   </si>
 </sst>
 </file>
@@ -159,8 +162,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D54ECB8E-769D-4A00-9DE3-82423EAFAADE}" name="_00_pa_ROSES" displayName="_00_pa_ROSES" ref="A1:D4" totalsRowShown="0" tableBorderDxfId="0">
-  <autoFilter ref="A1:D4" xr:uid="{D54ECB8E-769D-4A00-9DE3-82423EAFAADE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D54ECB8E-769D-4A00-9DE3-82423EAFAADE}" name="_00_pa_ROSES" displayName="_00_pa_ROSES" ref="A1:D5" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="A1:D5" xr:uid="{D54ECB8E-769D-4A00-9DE3-82423EAFAADE}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{2771186E-1735-445B-A922-68F7B197968B}" name="ss_id"/>
     <tableColumn id="2" xr3:uid="{0583B50A-6AAC-4F0E-82FC-808C604EA6E2}" name="identified_pa_studies"/>
@@ -488,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619D603B-AEB4-445D-A540-AA77EB3B3C97}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="23.85546875" customWidth="1"/>
@@ -541,6 +544,14 @@
         <v>234</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>292</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -550,15 +561,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -567,6 +569,15 @@
     <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -765,14 +776,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6320F81-7A8B-475D-BD32-B501228B4D65}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{835E6547-48E3-4AE1-A71D-3B61CA263E90}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -783,6 +786,29 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6320F81-7A8B-475D-BD32-B501228B4D65}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7747D71B-9149-48DF-A649-6E7ABE075555}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7747D71B-9149-48DF-A649-6E7ABE075555}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
+++ b/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3D703AA-CD71-4C29-8D6D-BF3C621E57D2}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB48A14-BF79-4B0D-A4AF-F4A2ED0B6824}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="30060" yWindow="1815" windowWidth="21600" windowHeight="11175" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
   </bookViews>
   <sheets>
     <sheet name="00_FOMD_Roses" sheetId="1" r:id="rId1"/>
@@ -551,6 +551,9 @@
       <c r="B5">
         <v>292</v>
       </c>
+      <c r="C5">
+        <v>274</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
+++ b/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
@@ -584,8 +584,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="14ce307a2e56825cff9c9e7fcaaeda24">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0503e52156abb22d20ee02405306de7b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1b97c7f6381d52e0ece85968e631718a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af6cb7be8893fd4f0d362fb6f7fa19cb" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
     <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
@@ -798,20 +798,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7747D71B-9149-48DF-A649-6E7ABE075555}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08EB30E9-ECA6-4B98-9C1A-BF551CD5EEB1}"/>
 </file>
--- a/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
+++ b/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="00_FOMD_Roses" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,10 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>MD_Rosen_24_Effec_Sc</t>
-  </si>
-  <si>
-    <t>MA_Sanch_22_Finan_Ec</t>
+    <t>ss_id</t>
   </si>
   <si>
     <t>identified_pa_studies</t>
@@ -53,7 +50,10 @@
     <t>pa_studies_after_screening</t>
   </si>
   <si>
-    <t>ss_id</t>
+    <t>MD_Rosen_24_Effec_Sc</t>
+  </si>
+  <si>
+    <t>MA_Sanch_22_Finan_Ec</t>
   </si>
   <si>
     <t>MD_Jones_21_A glo_Sc</t>
@@ -66,7 +66,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,28 +492,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619D603B-AEB4-445D-A540-AA77EB3B3C97}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
       </c>
       <c r="B2">
         <v>2147</v>
@@ -522,9 +522,9 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>119</v>
@@ -533,7 +533,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -544,7 +544,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -564,6 +564,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -572,15 +581,6 @@
     <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -779,22 +779,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{835E6547-48E3-4AE1-A71D-3B61CA263E90}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6320F81-7A8B-475D-BD32-B501228B4D65}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6320F81-7A8B-475D-BD32-B501228B4D65}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{835E6547-48E3-4AE1-A71D-3B61CA263E90}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
+++ b/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB48A14-BF79-4B0D-A4AF-F4A2ED0B6824}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A8EA8A6-555D-4EBC-BA9D-8C1B86CDDA11}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
   </bookViews>
   <sheets>
     <sheet name="00_FOMD_Roses" sheetId="1" r:id="rId1"/>
@@ -66,7 +66,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,7 +83,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -100,6 +100,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -136,6 +142,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,12 +499,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{619D603B-AEB4-445D-A540-AA77EB3B3C97}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="23.85546875" customWidth="1"/>
+    <col min="1" max="4" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,18 +518,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>2147</v>
-      </c>
-      <c r="C2">
-        <v>2130</v>
+        <v>1811</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1811</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -530,10 +537,10 @@
         <v>119</v>
       </c>
       <c r="C3">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -544,7 +551,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -564,15 +571,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
@@ -583,9 +581,9 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1b97c7f6381d52e0ece85968e631718a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="af6cb7be8893fd4f0d362fb6f7fa19cb" ns2:_="" ns3:_="">
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005BE3C66ACF4393458051577D36AC6C25" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4e0e0d96de7fb32b1678b66c28514d8e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b26243c-b736-4d9c-b036-479be2ad88a1" xmlns:ns3="432dd258-9dce-4cb3-b611-c68c0fbce7f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac451aab8c96dec805c937cbafca7133" ns2:_="" ns3:_="">
     <xsd:import namespace="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
     <xsd:import namespace="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
     <xsd:element name="properties">
@@ -604,6 +602,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -661,6 +660,11 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="19" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -778,14 +782,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6320F81-7A8B-475D-BD32-B501228B4D65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{835E6547-48E3-4AE1-A71D-3B61CA263E90}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{835E6547-48E3-4AE1-A71D-3B61CA263E90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FBE89F6-C0BF-4371-9920-F3F180969749}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08EB30E9-ECA6-4B98-9C1A-BF551CD5EEB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6320F81-7A8B-475D-BD32-B501228B4D65}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
+++ b/02.FOMD/02.metadata_structure/00_FOMD_ROSES.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/02.FOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A8EA8A6-555D-4EBC-BA9D-8C1B86CDDA11}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{2F06371F-12C4-490E-B574-5164683F72A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53690C58-3BA3-420A-88F4-D1795B08471F}"/>
   <bookViews>
     <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{83D602D3-2FE2-4AFC-A839-EADA8530BF7B}"/>
   </bookViews>
   <sheets>
     <sheet name="00_FOMD_Roses" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -548,7 +548,7 @@
         <v>237</v>
       </c>
       <c r="C4">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
